--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O252"/>
+  <dimension ref="A1:O254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -17777,6 +17777,110 @@
       <c r="O252" t="inlineStr">
         <is>
           <t>https://github.com/HUST-SLOW/DeCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, MPDD</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 偽跨模態匹配 (Pseudo Cross-Modal Matching)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>XMatchAD (Cross-Modal Matching Perspective on Reconstruction-based AD)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Mingxiu Cai, Zhe Zhang, Gaochang Wu, Tianyou Chai</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Transactions on Image Processing / arXiv 2607.23658 / PubMed 42555332)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2607.23658 HTML not accessible (egress blocked), GitHub code coming soon; candidate metrics from search snippets (not table-verified): MVTec I-AUROC≈98.7/P-AUROC≈98.2/P-AP≈68.9, VisA I-AUROC≈92.8/P-AUROC≈98.6/P-AP≈42.1, MPDD I-AUROC≈94.6/P-AUROC≈99.1/P-AP≈48.9 [基於重構/跨模態匹配]</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.23658</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>https://github.com/Mingxiu-Cai/XMatchAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (few-shot class-agnostic, NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 類別無關少樣本 (Class-Agnostic Few-shot AD) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>ResAD++ (Class-Agnostic Anomaly Detection via Residual Feature Learning)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Xincheng Yao, Chongyang Zhao, Guannan Jiang, Ziyan Wang, Guangtao Zhai, et al.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>IJCV 2026 (International Journal of Computer Vision / arXiv 2509.23741 / Springer 10.1007/s11263-026-02885-1)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; GitHub has ResAD (NeurIPS 2024) metrics only; candidate 8-shot: MVTec AD I-AUROC≈98.6/P-AUROC≈96.7 from search snippet; NON-STANDARD (class-agnostic k-shot, no target retraining) [類別無關少樣本]</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.23741</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>https://github.com/xcyao00/ResAD</t>
         </is>
       </c>
     </row>
@@ -17989,7 +18093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O135"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27022,6 +27126,110 @@
       <c r="O135" t="inlineStr">
         <is>
           <t>https://github.com/HUST-SLOW/DeCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 偽跨模態匹配 (Pseudo Cross-Modal Matching)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>XMatchAD (Cross-Modal Matching Perspective on Reconstruction-based AD)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Mingxiu Cai, Zhe Zhang, Gaochang Wu, Tianyou Chai</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Transactions on Image Processing / arXiv 2607.23658 / PubMed 42555332)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; GitHub code coming soon; candidate I-AUROC≈98.7/P-AUROC≈98.2/P-AP≈68.9 from search snippets [基於重構/跨模態匹配]</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.23658</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>https://github.com/Mingxiu-Cai/XMatchAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MVTec AD (few-shot class-agnostic, NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 類別無關少樣本 (Class-Agnostic Few-shot AD) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ResAD++ (Class-Agnostic Anomaly Detection via Residual Feature Learning)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Xincheng Yao, Chongyang Zhao, Guannan Jiang, Ziyan Wang, Guangtao Zhai, et al.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>IJCV 2026 (International Journal of Computer Vision / arXiv 2509.23741 / Springer 10.1007/s11263-026-02885-1)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; candidate 8-shot I-AUROC≈98.6/P-AUROC≈96.7 from search snippet; NON-STANDARD [類別無關少樣本]</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.23741</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>https://github.com/xcyao00/ResAD</t>
         </is>
       </c>
     </row>
@@ -30213,7 +30421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36185,6 +36393,110 @@
       <c r="O91" t="inlineStr">
         <is>
           <t>https://github.com/HUST-SLOW/DeCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 偽跨模態匹配 (Pseudo Cross-Modal Matching)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>XMatchAD (Cross-Modal Matching Perspective on Reconstruction-based AD)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mingxiu Cai, Zhe Zhang, Gaochang Wu, Tianyou Chai</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Transactions on Image Processing / arXiv 2607.23658 / PubMed 42555332)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; GitHub code coming soon; candidate I-AUROC≈92.8/P-AUROC≈98.6/P-AP≈42.1 from search snippets [基於重構/跨模態匹配]</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.23658</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://github.com/Mingxiu-Cai/XMatchAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VisA (few-shot class-agnostic, NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 類別無關少樣本 (Class-Agnostic Few-shot AD) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ResAD++ (Class-Agnostic Anomaly Detection via Residual Feature Learning)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Xincheng Yao, Chongyang Zhao, Guannan Jiang, Ziyan Wang, Guangtao Zhai, et al.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>IJCV 2026 (International Journal of Computer Vision / arXiv 2509.23741 / Springer 10.1007/s11263-026-02885-1)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; candidate metrics available in paper Table (k-shot settings); NON-STANDARD [類別無關少樣本]</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.23741</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://github.com/xcyao00/ResAD</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -37800,6 +38112,58 @@
       <c r="N24" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0031320325012440</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MPDD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / 偽跨模態匹配 (Pseudo Cross-Modal Matching)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>XMatchAD (Cross-Modal Matching Perspective on Reconstruction-based AD)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mingxiu Cai, Zhe Zhang, Gaochang Wu, Tianyou Chai</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IEEE TIP 2026 (IEEE Transactions on Image Processing / arXiv 2607.23658 / PubMed 42555332)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; GitHub code coming soon; candidate I-AUROC≈94.6/P-AUROC≈99.1/P-AP≈48.9 from search snippets [基於重構/跨模態匹配]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.23658</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://github.com/Mingxiu-Cai/XMatchAD</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O254"/>
+  <dimension ref="A1:O257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -15017,24 +15017,24 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
+          <t>MVTec AD, VisA (few-shot 1-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B204" s="18" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation)</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>SubspaceAD</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B204" s="18" t="inlineStr">
-        <is>
-          <t>基於表徵 (Representation)</t>
-        </is>
-      </c>
-      <c r="C204" s="18" t="inlineStr">
-        <is>
-          <t>SubspaceAD</t>
-        </is>
-      </c>
-      <c r="D204" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
           <t>CVPR 2026</t>
@@ -15050,14 +15050,26 @@
           <t>已發表</t>
         </is>
       </c>
-      <c r="H204" s="18" t="n"/>
-      <c r="I204" s="18" t="n"/>
-      <c r="J204" s="18" t="n"/>
-      <c r="K204" s="18" t="n"/>
+      <c r="H204" s="18" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I204" s="18" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="J204" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K204" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L204" s="18" t="n"/>
       <c r="M204" s="19" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SubspaceAD: Training-Free Few-Shot Anomaly Detection via Subspace Modeling</t>
+          <t>🟢 Few-shot verified — GitHub README (CLendering/SubspaceAD); MVTec AD 1-shot: I-AUROC=97.1, P-AUROC=97.5; VisA 1-shot: I-AUROC=93.2, P-AUROC=98.2; DINOv2-based training-free PCA subspace method; CVPR 2026. NON-STANDARD (few-shot 1-shot) — NOT comparable to standard unsupervised AD. Journal harvest update 2026-09-20. [基於表徵 / 少樣本 / Training-free]</t>
         </is>
       </c>
       <c r="N204" s="20" t="inlineStr">
@@ -17881,6 +17893,176 @@
       <c r="O254" t="inlineStr">
         <is>
           <t>https://github.com/xcyao00/ResAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (few-shot 1/2/4-shot, NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>基於 VLM/CLIP (CLIP-based) / 少樣本 (Few-shot)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>DriftAD (Visually-Guided Text Drift for Few-Shot IAD)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Wenyang Liu, Tianyi Liu, Dongshuo Zhang, Kejun Wu, Adams Wai-Kin Kong</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>ACM MM 2026 / arXiv 2608.23723</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I255" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>🟢 Few-shot verified — GitHub README (wenyang001/DriftAD); MVTec AD 1-shot: I-AUROC=97.2, P-AUROC=96.8, PRO=92.2; 4-shot: I-AUROC=98.0, P-AUROC=97.2, PRO=92.7; VisA 1-shot: I-AUROC=93.1, P-AUROC=97.4, PRO=86.7; 4-shot: I-AUROC=94.0, P-AUROC=98.0, PRO=88.3; OpenCLIP ViT-H/14; NON-STANDARD (few-shot 1/2/4-shot) — NOT comparable to standard unsupervised AD. ACM MM 2026 harvest 2026-09-20. [基於 VLM/CLIP / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2608.23723</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>https://github.com/wenyang001/DriftAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, Real-IAD, MVTec 3D-AD, MVTec LOCO</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 測試時適應 (Test-Time Adaptation) / 拓樸感知 (Topology-Aware)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TopoTTA (Learning Topology-Aware Representations via TTA for Anomaly Segmentation)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Ali Zia, Usman Ali, Abdul Rehman, Umer Ramzan, Kang Han, Muhammad Faheem, Shahnawaz Qureshi, Wei Xiang</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2026 (Early Access) / arXiv 2606.28268 / DOI 10.1109/TPAMI.2026.3710196 / PubMed 42397999</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>⏳ Pending — IEEE TPAMI 2026 Early Access (DOI 10.1109/TPAMI.2026.3710196, published 2026-07-03); arXiv 2606.28268; PubMed 42397999; arXiv HTML blocked — cannot directly verify Table I; search snippet cites backbone-dependent results: w/ Dinomaly: MVTec I-AUROC≈99.6/P-AUROC≈98.4/PRO≈94.8; VisA I-AUROC≈98.7/P-AUROC≈98.7/PRO≈94.5 (NOT standalone TopoTTA metrics — backbone-dependent TTA post-processing). Key claim: +15% avg F1 over SOTA across 6 benchmarks via persistent homology TTA. Project page: topotta.github.io. IEEE TPAMI journal harvest 2026-09-20. [基於表徵 / TTA / 拓樸感知]</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.28268</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>https://topotta.github.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, BTAD (cross-dataset zero-shot protocol)</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>基於 VLM/CLIP (CLIP-based) / SAM輔助 (SAM-assisted) / 零樣本 (Zero-shot)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>PSMP-CLIP (Patch-Prompt SAM and Multi-Semantic Prompting for CLIP-Based Zero-Shot AD)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.16785</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>arXiv 2609.16785 (2026-09-15)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.16785 (Sept 15, 2026); zero-shot cross-dataset protocol (trained on VisA→evaluated on MVTec AD and others); search snippet reports MVTec AD P-AUROC≈93.7 (cross-dataset zero-shot — NOT comparable to standard unsupervised AD); ViT-L-14-336 CLIP + SAM2.1; 14 datasets; no GitHub found as of 2026-09-20. NON-STANDARD (cross-dataset zero-shot). [基於 VLM/CLIP / SAM輔助 / 零樣本]</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.16785</t>
         </is>
       </c>
     </row>
@@ -18093,7 +18275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27230,6 +27412,129 @@
       <c r="O137" t="inlineStr">
         <is>
           <t>https://github.com/xcyao00/ResAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MVTec AD (few-shot 1-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>基於 VLM/CLIP (CLIP-based) / 少樣本 (Few-shot)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DriftAD (Visually-Guided Text Drift for Few-Shot IAD)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Wenyang Liu, Tianyi Liu, Dongshuo Zhang, Kejun Wu, Adams Wai-Kin Kong</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ACM MM 2026 / arXiv 2608.23723</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I138" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>🟢 Few-shot verified — GitHub README (wenyang001/DriftAD); 1-shot I-AUROC=97.2, P-AUROC=96.8, PRO=92.2; 4-shot I-AUROC=98.0/97.2/92.7; NON-STANDARD: few-shot protocol, NOT comparable to standard unsupervised AD. [基於 VLM/CLIP / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2608.23723</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>https://github.com/wenyang001/DriftAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MVTec AD (TTA post-processing; backbone-dependent; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 測試時適應 (Test-Time Adaptation)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TopoTTA (Learning Topology-Aware Representations via TTA for Anomaly Segmentation)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Ali Zia, Usman Ali, Abdul Rehman, Umer Ramzan, Kang Han, Muhammad Faheem, Shahnawaz Qureshi, Wei Xiang</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2026 (Early Access) / arXiv 2606.28268</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; search snippet cites w/ Dinomaly backbone: I-AUROC≈99.6/P-AUROC≈98.4/PRO≈94.8; backbone-dependent TTA — NOT standalone method. [TTA / 拓樸感知]</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.28268</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>https://topotta.github.io/</t>
         </is>
       </c>
     </row>
@@ -30421,7 +30726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36497,6 +36802,129 @@
       <c r="O93" t="inlineStr">
         <is>
           <t>https://github.com/xcyao00/ResAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>VisA (few-shot 1-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>基於 VLM/CLIP (CLIP-based) / 少樣本 (Few-shot)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DriftAD (Visually-Guided Text Drift for Few-Shot IAD)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Wenyang Liu, Tianyi Liu, Dongshuo Zhang, Kejun Wu, Adams Wai-Kin Kong</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ACM MM 2026 / arXiv 2608.23723</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I94" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>🟢 Few-shot verified — GitHub README (wenyang001/DriftAD); 1-shot I-AUROC=93.1, P-AUROC=97.4, PRO=86.7; 4-shot I-AUROC=94.0/98.0/88.3; NON-STANDARD: few-shot protocol. [基於 VLM/CLIP / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2608.23723</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>https://github.com/wenyang001/DriftAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VisA (TTA post-processing; backbone-dependent; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation) / 測試時適應 (Test-Time Adaptation)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TopoTTA (Learning Topology-Aware Representations via TTA for Anomaly Segmentation)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ali Zia, Usman Ali, Abdul Rehman, Umer Ramzan, Kang Han, Muhammad Faheem, Shahnawaz Qureshi, Wei Xiang</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>IEEE TPAMI 2026 (Early Access) / arXiv 2606.28268</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; search snippet cites w/ Dinomaly: I-AUROC≈98.7/P-AUROC≈98.7/PRO≈94.5; backbone-dependent TTA. [TTA / 拓樸感知]</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.28268</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://topotta.github.io/</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O257"/>
+  <dimension ref="A1:O262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18063,6 +18063,241 @@
       <c r="N257" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.16785</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, Real-IAD</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / Swin Transformer V2</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SwinAD (Multi-stage Feature Reconstruction for Unsupervised Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Huong Ninh, Chien Thai, Mai Xuan Trang, Vu-Minh Le, Thanh Ha Le, Long Tran</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>arXiv 2607.14534 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2607.14534 (Jul 16, 2026); arXiv HTML blocked, no GitHub repo found; web-search snippet from arXiv HTML: MVTec AD I-AUROC≈99.4%, I-AP≈99.7% (not directly verified from authoritative table). Frozen Swin Transformer V2 encoder + feature-diversity-preserving reconstruction decoder; stage-wise bottleneck dropout; MVTec AD, VisA, Real-IAD benchmarks. No journal affiliation confirmed. Journal harvest 2026-09-27. [基於重構 / Swin Transformer]</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.14534</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, Real-IAD, MVTec 3D-AD, COCO-AD, Uni-Medical</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>基於 Mamba/SSM (State Space Model-based) / 重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>MambaADv2 (Evolving Duality-enhanced State Space Model for Unsupervised AD)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>see arXiv 2606.23126</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>arXiv 2606.23126 (2026-06-22)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2606.23126 (Jun 22, 2026); arXiv HTML blocked, no GitHub repo found; web-search snippet: MVTec AD I-AUROC≈99.2%, mAD=87.2 (composite metric), VisA mAD=80.1; not directly verified from authoritative table. Duality-enhanced State Space (DSS) modules; 6 benchmarks: MVTec AD, VisA, Real-IAD, MVTec 3D-AD, COCO-AD, Uni-Medical. No journal affiliation confirmed. Journal harvest 2026-09-27. [基於 Mamba/SSM / 重構]</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.23126</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (task-free continual learning protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>持續學習 (Continual Learning) / 神經坍縮引導 (Neural-Collapse-guided) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>NC-TFAD (Neural-Collapse-guided Task-Free Continual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Xiaotong Kong, Chaoyang Song, Ziai Zhou, Jinxia Zhang, Kanjian Zhang, Haikun Wei (Southeast University)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03406 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.03406 (Sep 3, 2026); arXiv HTML blocked, no GitHub repo found; web-search snippet: MVTec AD I-AUROC≈82.1% in task-free continual learning setting (NOT comparable to standard unsupervised AD — continual protocol). Neural-collapse-inspired geometry-driven framework; Focal Neural Collapse Contrastive (FNCC) loss; MVTec AD and VisA datasets under task-free continual learning protocol. NON-STANDARD: continual learning protocol — NOT comparable to standard unsupervised AD. No journal affiliation confirmed. Journal harvest 2026-09-27. [持續學習 / 神經坍縮引導]</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03406</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (few-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>基於 VFM/基礎模型 (Vision Foundation Model) / 少樣本 (Few-shot) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>PL-SCEA (Power-Law Self-Correlation Enhanced Attention for Few-Shot Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Xiaoyu Yang, Qixing Wu, Huixian Zhao, Changlong Jin</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03655 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.03655 (Sep 3, 2026); arXiv HTML blocked, no GitHub repo found; no specific metrics in search snippets. Reconfigures pretrained attention of VFMs for few-shot industrial AD; Power-Law Self-Correlation Enhanced Attention (PL-SCEA); token-adaptive self-correlations over contextualized value features; MVTec AD and VisA under few-shot settings. NON-STANDARD: few-shot protocol — NOT comparable to standard unsupervised AD. No journal affiliation confirmed. Journal harvest 2026-09-27. [VFM / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03655</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>MVTec AD (object-class subset)</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>基於理論/貝葉斯 (Bayesian/Theoretical) / 無監督 AD</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>PrincipalUAD (A Principled Approach to Unsupervised Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>James Myles, Matthew Baugh, Johanna P. Müller, Bernhard Kainz, Yingzhen Li</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>arXiv 2609.21800 (2026-09-18)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.21800 (Sep 18, 2026); arXiv HTML blocked, no GitHub repo found; web-search snippet: improves MVTec AD object-class AUROC by 2.3% via adapting the underlying corruption model (exact absolute AUROC not confirmed from authoritative table). Reformulates UAD as Bayesian inverse problem; probabilistic anomaly score as energy of inferred corruption parameters; derives existing methods as special cases. Evaluated on MVTec AD (object-class subset). No journal affiliation confirmed. Journal harvest 2026-09-27. [基於理論/貝葉斯]</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.21800</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -27535,6 +27770,241 @@
       <c r="O139" t="inlineStr">
         <is>
           <t>https://topotta.github.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / Swin Transformer V2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SwinAD (Multi-stage Feature Reconstruction for Unsupervised Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Huong Ninh, Chien Thai, Mai Xuan Trang, Vu-Minh Le, Thanh Ha Le, Long Tran</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>arXiv 2607.14534 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-search snippet: I-AUROC≈99.4%, I-AP≈99.7% (not directly verified). [基於重構]</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.14534</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>基於 Mamba/SSM (State Space Model-based) / 重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MambaADv2 (Evolving Duality-enhanced State Space Model for Unsupervised AD)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>see arXiv 2606.23126</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>arXiv 2606.23126 (2026-06-22)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-search snippet: I-AUROC≈99.2%, mAD=87.2 (mAD is composite, not standard I-AUROC). [基於 Mamba/SSM]</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.23126</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MVTec AD (task-free continual learning protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>持續學習 (Continual Learning) / 神經坍縮引導 (Neural-Collapse-guided) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NC-TFAD (Neural-Collapse-guided Task-Free Continual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Xiaotong Kong, Chaoyang Song, Ziai Zhou, Jinxia Zhang, Kanjian Zhang, Haikun Wei (Southeast University)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03406 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-search snippet: I-AUROC≈82.1% (continual setting). NON-STANDARD: task-free continual learning — NOT comparable to standard unsupervised AD. [持續學習]</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03406</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MVTec AD (few-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>基於 VFM/基礎模型 (Vision Foundation Model) / 少樣本 (Few-shot) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PL-SCEA (Power-Law Self-Correlation Enhanced Attention for Few-Shot Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Xiaoyu Yang, Qixing Wu, Huixian Zhao, Changlong Jin</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03655 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; no specific metrics found. NON-STANDARD: few-shot protocol. [VFM / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03655</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MVTec AD (object-class subset)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>基於理論/貝葉斯 (Bayesian/Theoretical) / 無監督 AD</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PrincipalUAD (A Principled Approach to Unsupervised Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>James Myles, Matthew Baugh, Johanna P. Müller, Bernhard Kainz, Yingzhen Li</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>arXiv 2609.21800 (2026-09-18)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; snippet: +2.3% object-class AUROC (absolute value not confirmed). Bayesian inverse problem formulation. [基於理論/貝葉斯]</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.21800</t>
         </is>
       </c>
     </row>
@@ -30726,7 +31196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -36925,6 +37395,194 @@
       <c r="O95" t="inlineStr">
         <is>
           <t>https://topotta.github.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>基於重構 (Reconstruction-based) / Swin Transformer V2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SwinAD (Multi-stage Feature Reconstruction for Unsupervised Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Huong Ninh, Chien Thai, Mai Xuan Trang, Vu-Minh Le, Thanh Ha Le, Long Tran</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>arXiv 2607.14534 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; no specific VisA metrics in search snippets. [基於重構]</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.14534</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>基於 Mamba/SSM (State Space Model-based) / 重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MambaADv2 (Evolving Duality-enhanced State Space Model for Unsupervised AD)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>see arXiv 2606.23126</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>arXiv 2606.23126 (2026-06-22)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-search snippet: VisA mAD=80.1 (composite metric, not standard I-AUROC). [基於 Mamba/SSM]</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.23126</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VisA (task-free continual learning protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>持續學習 (Continual Learning) / 神經坍縮引導 (Neural-Collapse-guided) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NC-TFAD (Neural-Collapse-guided Task-Free Continual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Xiaotong Kong, Chaoyang Song, Ziai Zhou, Jinxia Zhang, Kanjian Zhang, Haikun Wei (Southeast University)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03406 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; no specific VisA metrics in snippets (continual protocol). NON-STANDARD: task-free continual learning. [持續學習]</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03406</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VisA (few-shot; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>基於 VFM/基礎模型 (Vision Foundation Model) / 少樣本 (Few-shot) — NON-STANDARD PROTOCOL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PL-SCEA (Power-Law Self-Correlation Enhanced Attention for Few-Shot Industrial AD)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Xiaoyu Yang, Qixing Wu, Huixian Zhao, Changlong Jin</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>arXiv 2609.03655 (2026-09-03)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; no specific VisA metrics. NON-STANDARD: few-shot. [VFM / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.03655</t>
         </is>
       </c>
     </row>
@@ -40594,7 +41252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -42186,6 +42844,53 @@
       <c r="N24" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.20300</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MVTec 3D-AD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>基於 Mamba/SSM (State Space Model-based) / 重構 (Reconstruction)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MambaADv2 (Evolving Duality-enhanced State Space Model for Unsupervised AD)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>see arXiv 2606.23126</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>arXiv 2606.23126 (2026-06-22)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; no specific MVTec 3D metrics in search snippets. [基於 Mamba/SSM]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.23126</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O262"/>
+  <dimension ref="A1:O266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18298,6 +18298,194 @@
       <c r="N262" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.21800</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>MVTec 3D-AD, Eyecandies</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>基於 3D/RGB-D (3D/RGB-D-based) / 幾何先驗 (Geometric Prior) / 點雲 (Point Cloud)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>GPAD (Multimodal Industrial Anomaly Detection via Geometric Prior)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Min Li, Jinghui He, Gang Li, Jiachen Li, Jin Wan, Delong Han</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2026 (accepted) / arXiv 2603.22757 (2026-03-24)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2603.22757 (Mar 24, 2026); accepted IEEE Transactions on Circuits and Systems for Video Technology (TCSVT). arXiv HTML blocked, no GitHub repo found. Proposes point cloud expert model with differential normal vector computation for fine-grained geometric feature extraction + two-stage fusion strategy (attention fusion + anomaly region segmentation based on geometric prior). PyTorch 1.13.1, RTX 4090, batch 8, 200 epochs. "Outperforms SOTA on MVTec 3D-AD and Eyecandies" (no specific AUROC accessible). Journal harvest 2026-10-04. [基於 3D/RGB-D / 幾何先驗 / 點雲]</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22757</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, Real-IAD</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 特徵傳輸曲率 (Feature Transport Curvature / Holonomy)</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>GaugeDefect (Detecting Surface Anomalies by Curvature of Feature Transport)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.13282</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>arXiv 2609.13282 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.13282 (Sep 2026); arXiv HTML blocked, no GitHub repo found. Gauge-theoretic method: extracts spatial feature lattice from pretrained backbone, estimates local feature frames, measures feature-transport curvature (holonomy around closed loops); anomaly map from loop curvature calibrated with normal statistics. Gains clearest on localization-sensitive metrics (P-AP, AUPRO). Web-search snippet AUPRO (NOT verified from authoritative table): MVTec AD 96.5 / VisA 95.1 / Real-IAD 94.4. Journal harvest 2026-10-04. [基於表徵 / 特徵傳輸曲率]</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.13282</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>MVTec LOCO (training-free zero-shot protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / 訓練免費 (Training-Free) / 邏輯+結構異常 (Logical+Structural AD)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>CalibFusion-AD (Training-Free Logical and Structural Anomaly Detection via Calibrated Fusion)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Changyi Li, Miao Yu, Kai Dong, Yu Xiao (Aalto University / Harbin Engineering University)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>arXiv 2609.05091 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.05091 (Sep 2026); arXiv HTML blocked, no GitHub repo found. Training-free approach that introduces counting ability for logical anomaly detection; normal-set calibration aligns heterogeneous anomaly cues (structural + logical) without additional training or part-level supervision. Best among training-free detectors on MVTec LOCO. Web-search snippet MVTec LOCO AUROC (NOT verified): logical 89.0 / structural 95.9 / avg 92.5. NON-STANDARD (training-free/zero-shot protocol; not comparable to trained standard AD). Journal harvest 2026-10-04. [基於基礎模型 / 訓練免費 / 邏輯+結構]</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.05091</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, BTAD, KSDD, Real-IAD (zero-shot cross-domain protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / CLIP + DINOv3 / 記憶庫 (Memory Bank) / 零樣本跨域 (Zero-Shot Cross-Domain)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>LUMIN (Lightweight Universal Manufacturing Inspection Network for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.04775</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>arXiv 2609.04775 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2609.04775 (Sep 2026); arXiv HTML blocked, no GitHub repo found. Engineering efficiency focus: PSP (Plugin Sampler Pipeline) — adaptive memory bank sampling with zero backbone forward passes (341× faster than FPS); parallel memory bank similarity computation (reduces inference memory/latency by &gt;95%); stratified pixel sampling (20× evaluation speedup). Zero-shot cross-domain protocol: trained on VisA, tested on MVTec-AD, BTAD, KSDD, Real-IAD without fine-tuning; VisA evaluated with model trained on MVTec-AD. Frozen CLIP + DINOv3 backbones, input 518×518 + 512×512, layers 6/12/18/24. NON-STANDARD (cross-domain zero-shot; not comparable to standard AD benchmarks). No dataset-specific metrics available. Journal harvest 2026-10-04. [基於基礎模型 / CLIP + DINOv3 / 記憶庫 / 零樣本跨域]</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.04775</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O144"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28005,6 +28193,100 @@
       <c r="N144" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.21800</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MVTec AD</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 特徵傳輸曲率 (Feature Transport Curvature / Holonomy)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GaugeDefect (Detecting Surface Anomalies by Curvature of Feature Transport)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.13282</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>arXiv 2609.13282 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-snippet AUPRO≈96.5 on MVTec AD (NOT verified). [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.13282</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MVTec AD (zero-shot cross-domain protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / CLIP + DINOv3 / 零樣本跨域 (Zero-Shot Cross-Domain)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LUMIN (Lightweight Universal Manufacturing Inspection Network for Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.04775</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>arXiv 2609.04775 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; zero-shot cross-domain protocol (trained on VisA→tested on MVTec AD). No specific metrics found. NON-STANDARD. [基於基礎模型 / CLIP+DINOv3 / 零樣本跨域]</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.04775</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -29811,6 +30093,53 @@
       <c r="N26" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.inffus.2026.S156625352600093X</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MVTec LOCO (training-free zero-shot protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / 訓練免費 (Training-Free) / 邏輯+結構異常 (Logical+Structural AD)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CalibFusion-AD (Training-Free Logical and Structural Anomaly Detection via Calibrated Fusion)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Changyi Li, Miao Yu, Kai Dong, Yu Xiao (Aalto / Harbin EUT)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>arXiv 2609.05091 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-snippet avg AUROC≈92.5 (logical 89.0, structural 95.9) on MVTec LOCO (NOT verified; training-free NON-STANDARD protocol). [基於基礎模型 / 訓練免費]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.05091</t>
         </is>
       </c>
     </row>
@@ -31196,7 +31525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -37583,6 +37912,53 @@
       <c r="N99" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.03655</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>VisA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>基於表徵 (Representation-based) / 特徵傳輸曲率 (Feature Transport Curvature / Holonomy)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GaugeDefect (Detecting Surface Anomalies by Curvature of Feature Transport)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>see arXiv 2609.13282</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>arXiv 2609.13282 (2026-09)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked; web-snippet AUPRO≈95.1 on VisA (NOT verified). [基於表徵]</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.13282</t>
         </is>
       </c>
     </row>
@@ -41252,7 +41628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -42891,6 +43267,53 @@
       <c r="N25" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.23126</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MVTec 3D-AD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>基於 3D/RGB-D (3D/RGB-D-based) / 幾何先驗 (Geometric Prior) / 點雲 (Point Cloud)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GPAD (Multimodal Industrial Anomaly Detection via Geometric Prior)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Min Li, Jinghui He, Gang Li, Jiachen Li, Jin Wan, Delong Han</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IEEE TCSVT 2026 (accepted) / arXiv 2603.22757 (2026-03-24)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv HTML blocked, no GitHub; "outperforms SOTA on MVTec 3D-AD". IEEE TCSVT accepted. [基於 3D/RGB-D / 幾何先驗]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.22757</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O266"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18486,6 +18486,152 @@
       <c r="N266" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.04775</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (few-shot cross-dataset protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>基於視覺語言模型 (VLM-based) / CLIP / 非對稱提示自適應 (Asymmetric Prompt Adaptation) / 少樣本 (Few-Shot)</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Anchor and Adapt (Asymmetric Prompt Adaptation for Few-Shot Industrial Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Mengyang Zhao, Teng Fu, Haiyang Yu, Ke Niu, Bin Li, Xiangyang Xue</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>arXiv 2610.07016 (2026-10-04)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2610.07016 (Oct 4, 2026); arXiv HTML blocked, no GitHub repo found. Two-stage prompt learning framework: Stage I learns transferable normal/abnormal text anchors from annotated auxiliary data; Stage II freezes anchors and adapts an additional normal branch using few target normal images. Text-anchor regularization keeps adapted prompts consistent with generic normal prior and separated from abnormal anchors. Evaluates cross-dataset transfer in both directions between MVTec AD and VisA under 1-, 2-shot settings. Competes with PromptAD and template-based prompt methods. NON-STANDARD PROTOCOL (few-shot). Journal harvest 2026-10-11. [基於VLM/CLIP / 非對稱提示自適應 / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.07016</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>MVTec AD 2, Kaputt 2 (VAND 4.0 Challenge benchmark report; CVPR 2026 workshop)</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>基準/挑戰賽報告 (Benchmark / Challenge Report) — MVTec AD 2 工業缺陷分割 + Kaputt 2 零售物流</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>VAND 4.0 Challenge Report (Detecting Defects that Matter: An Application-Driven Benchmark)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>MVTec, TUM, Amazon, Intel, NVIDIA (VAND 4.0 organizing committee)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>CVPR 2026 VAND 4.0 Workshop / arXiv 2610.04392 (2026-10-03)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2610.04392 (Oct 3, 2026); CVPR 2026 VAND 4.0 Workshop challenge report. Industrial Track: MVTec AD 2, scored by pixel-level SegF1 (NOT AUROC). Regular setting: 9 submissions; best ~57% SegF1. Zero-shot: 5 submissions; trails by ~15 SegF1 pts. DINOv3 backbones dominate. Robustness to distribution shift flagged as open problem. Retail Track: Kaputt 2, scored by AP_any; supervised near-saturation for common defects; rare defect performance collapses (spillage ~53 AP, missing units ~27 AP). NOT a method paper — catalog reference entry. Journal harvest 2026-10-11. [基準/挑戰賽報告]</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.04392</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>https://github.com/cvpr-vand/vand-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA, MPDD, DTD, SDD (零樣本開放詞彙協議; NON-STANDARD PROTOCOL — open-vocabulary zero-shot)</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / VLM / 代理工具增強 (Agentic Tools) / 開放詞彙 (Open-Vocabulary) / 零樣本</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>IndusAgent (Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Rongbin Tan, Huawei Cao, Shuhan Song et al. (13 authors)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>arXiv 2605.20682 (2026-05-20)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2605.20682 (May 20, 2026); arXiv HTML blocked, no GitHub found. Tool-augmented agentic framework for open-vocabulary IAD. Fine-tuned on custom Indus-CoT dataset with gated reinforcement learning objective (classification + localization + anomaly reasoning + tool usage). Uses dynamic region cropping, high-frequency feature enhancement, prior retrieval. Evaluates: MVTec-AD, VisA, MPDD, DTD, SDD — zero-shot protocol. Headline: avg score 83.4% (metric unclear from web snippet; NOT verified). NON-STANDARD PROTOCOL (open-vocabulary zero-shot). Previously missed in Aug/Sep harvests. Journal harvest 2026-10-11. [基於基礎模型/VLM / 代理工具增強 / 開放詞彙 / 零樣本]</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
     </row>
@@ -18698,7 +18844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28287,6 +28433,53 @@
       <c r="N146" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.04775</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MVTec AD (few-shot cross-dataset protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>基於視覺語言模型 (VLM-based) / CLIP / 非對稱提示自適應 / 少樣本 (Few-Shot)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Anchor and Adapt (Asymmetric Prompt Adaptation for Few-Shot Industrial Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Mengyang Zhao, Teng Fu, Haiyang Yu, Ke Niu, Bin Li, Xiangyang Xue</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>arXiv 2610.07016 (2026-10-04)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>⏳ Pending — few-shot cross-dataset protocol. arXiv HTML blocked; metrics not accessible. [基於VLM/CLIP / 非對稱提示自適應 / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.07016</t>
         </is>
       </c>
     </row>
@@ -30180,7 +30373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -31486,6 +31679,58 @@
       <c r="O19" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MVTec AD 2 (VAND 4.0 Challenge; pixel-level SegF1 metric — NOT AUROC)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>基準/挑戰賽報告 (Benchmark / Challenge Report)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VAND 4.0 Challenge Report (Detecting Defects that Matter: Application-Driven Benchmark)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MVTec, TUM, Amazon, Intel, NVIDIA (VAND 4.0 organizing committee)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CVPR 2026 VAND 4.0 Workshop / arXiv 2610.04392 (2026-10-03)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⏳ Pending — benchmark/challenge report. MVTec AD 2 Industrial Track. Primary metric: pixel-level SegF1 (NOT AUROC). Best regular-setting entry: ~57% SegF1. Zero-shot entries trail by ~15 SegF1 pts. DINOv3 backbones dominate. Full leaderboard on benchmark.mvtec.com. NOT a standalone method paper. [基準/挑戰賽報告]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.04392</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://github.com/cvpr-vand/vand-2026</t>
         </is>
       </c>
     </row>
@@ -31525,7 +31770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -37959,6 +38204,100 @@
       <c r="N100" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2609.13282</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>VisA (few-shot cross-dataset protocol; NON-STANDARD PROTOCOL)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>基於視覺語言模型 (VLM-based) / CLIP / 非對稱提示自適應 / 少樣本 (Few-Shot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Anchor and Adapt (Asymmetric Prompt Adaptation for Few-Shot Industrial Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Mengyang Zhao, Teng Fu, Haiyang Yu, Ke Niu, Bin Li, Xiangyang Xue</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>arXiv 2610.07016 (2026-10-04)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>⏳ Pending — few-shot cross-dataset protocol. arXiv HTML blocked; metrics not accessible. [基於VLM/CLIP / 非對稱提示自適應 / 少樣本]</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.07016</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VisA (零樣本開放詞彙協議; NON-STANDARD PROTOCOL — open-vocabulary zero-shot)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / VLM / 代理工具增強 (Agentic Tools) / 開放詞彙 / 零樣本</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IndusAgent (Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Rongbin Tan, Huawei Cao, Shuhan Song et al.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>arXiv 2605.20682 (2026-05-20)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>⏳ Pending — open-vocabulary zero-shot protocol. arXiv HTML blocked; metrics not accessible. [基於基礎模型/VLM / 代理 / 零樣本]</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
     </row>
@@ -38060,7 +38399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -39626,6 +39965,53 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>https://github.com/Mingxiu-Cai/XMatchAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MPDD (零樣本開放詞彙協議; NON-STANDARD PROTOCOL — open-vocabulary zero-shot)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>基於基礎模型 (Foundation Model-based) / VLM / 代理工具增強 (Agentic Tools) / 開放詞彙 / 零樣本</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IndusAgent (Reinforcing Open-Vocabulary Industrial Anomaly Detection with Agentic Tools)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rongbin Tan, Huawei Cao, Shuhan Song et al.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>arXiv 2605.20682 (2026-05-20)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⏳ Pending — open-vocabulary zero-shot protocol. arXiv HTML blocked; metrics not accessible. [基於基礎模型/VLM / 代理 / 零樣本]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.20682</t>
         </is>
       </c>
     </row>

--- a/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
+++ b/AnomalyDetection_Papers_Summary_v10_20260425.xlsx
@@ -1133,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O269"/>
+  <dimension ref="A1:O271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -18632,6 +18632,100 @@
       <c r="N269" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2605.20682</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MVTec AD, VisA (異常合成框架; 評估下游 AD 效果)</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>基於異常合成 (Anomaly Synthesis-based) / 基礎模型/大型多模態模型 (Foundation Model / LMM-based) / 自監督提示優化 (Self-Supervised Prompt Optimization)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>CORE (Contrast-and-Reflect for Self-Supervised Prompt Optimization in Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Haoxiang Rao, Fang Zhao, Zhao Wang, Weijia Li, Chenyang Si, Caifeng Shan</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>arXiv 2610.19610 (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2610.19610 (Oct 14, 2026); arXiv HTML blocked, no GitHub repo found. Training-free self-supervised prompt optimization framework for anomaly synthesis using large multimodal models (LMMs). Proposes an Anomaly Context Grounding (ACG) module to generate location-conditioned prompts, and a Contrast-and-Reflect (CoR) step that iteratively refines prompts by contrasting synthesized anomalies against normal regions in a self-supervised loop. Covers both zero-shot and one-shot anomaly synthesis settings. Evaluates by measuring downstream AD performance gains on MVTec-AD and VisA benchmarks. Method improves synthesis quality for downstream detectors; specific I-AUROC/P-AUROC values for the downstream detector not accessible (arXiv blocked). Journal harvest 2026-10-18. [基於異常合成 / 基礎模型/LMM / 自監督提示優化]</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.19610</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MVTec AD (15 tasks), VisA (12 tasks) (持續學習基準; NON-STANDARD PROTOCOL — 持續/漸進學習)</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>基準/評測論文 (Benchmark Paper) / 持續學習 (Continual Learning) / 工業視覺異常偵測</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>InCLAD (A Continual Learning Benchmark for Industrial Visual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Łukasz Marcjan, Dorota Wilk-Kołodziejczyk, Roberto Corizzo</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>arXiv 2610.15032 (2026-10-10)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>⏳ Pending — arXiv 2610.15032 (Oct 10, 2026); arXiv HTML blocked. Benchmark paper defining continual learning evaluation protocols for industrial VAD. Task-incremental setup: each industrial component is a separate task; training is semi-supervised (normal images only). Defines three continual scenarios: Random, Easy-to-Hard, and Hard-to-Easy task orderings, plus cross-dataset scenarios. Key challenge: catastrophic forgetting. Evaluates existing AD methods (standard and continual) on MVTec AD (15 tasks) and VisA (12 tasks). NOT a method paper — catalog reference entry for benchmark evaluation protocol. NON-STANDARD PROTOCOL (continual/incremental learning). Journal harvest 2026-10-18. [基準/評測 / 持續學習]</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.15032</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -28480,6 +28574,100 @@
       <c r="N147" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2610.07016</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MVTec AD (異常合成框架; 評估下游 AD 效果)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>基於異常合成 (Anomaly Synthesis-based) / 基礎模型/LMM (Foundation Model / LMM-based) / 自監督提示優化 (Self-Supervised Prompt Optimization)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CORE (Contrast-and-Reflect for Self-Supervised Prompt Optimization in Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Haoxiang Rao, Fang Zhao, Zhao Wang, Weijia Li, Chenyang Si, Caifeng Shan</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>arXiv 2610.19610 (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>⏳ Pending — anomaly synthesis framework; downstream AD metrics not accessible (arXiv blocked). [基於異常合成 / 基礎模型/LMM / 自監督提示優化]</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.19610</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MVTec AD (15 tasks, 持續學習基準; NON-STANDARD PROTOCOL — 持續/漸進學習)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>基準/評測論文 (Benchmark Paper) / 持續學習 (Continual Learning)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>InCLAD (A Continual Learning Benchmark for Industrial Visual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Łukasz Marcjan, Dorota Wilk-Kołodziejczyk, Roberto Corizzo</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>arXiv 2610.15032 (2026-10-10)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>⏳ Pending — continual learning benchmark on MVTec AD 15 tasks. arXiv HTML blocked; per-method forgetting/accuracy metrics not accessible. NOT comparable to standard unsupervised AD. [基準/評測 / 持續學習]</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.15032</t>
         </is>
       </c>
     </row>
@@ -31770,7 +31958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -38298,6 +38486,100 @@
       <c r="N102" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2605.20682</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VisA (異常合成框架; 評估下游 AD 效果)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>基於異常合成 (Anomaly Synthesis-based) / 基礎模型/LMM (Foundation Model / LMM-based) / 自監督提示優化 (Self-Supervised Prompt Optimization)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CORE (Contrast-and-Reflect for Self-Supervised Prompt Optimization in Anomaly Synthesis)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Haoxiang Rao, Fang Zhao, Zhao Wang, Weijia Li, Chenyang Si, Caifeng Shan</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>arXiv 2610.19610 (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>⏳ Pending — anomaly synthesis framework; downstream AD metrics not accessible (arXiv blocked). [基於異常合成 / 基礎模型/LMM / 自監督提示優化]</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.19610</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VisA (12 tasks, 持續學習基準; NON-STANDARD PROTOCOL — 持續/漸進學習)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>基準/評測論文 (Benchmark Paper) / 持續學習 (Continual Learning)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>InCLAD (A Continual Learning Benchmark for Industrial Visual Anomaly Detection)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Łukasz Marcjan, Dorota Wilk-Kołodziejczyk, Roberto Corizzo</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>arXiv 2610.15032 (2026-10-10)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>⏳ Pending</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>⏳ Pending — continual learning benchmark on VisA 12 tasks. arXiv HTML blocked; metrics not accessible. NOT comparable to standard unsupervised AD. [基準/評測 / 持續學習]</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2610.15032</t>
         </is>
       </c>
     </row>
